--- a/outputs/60-7.xlsx
+++ b/outputs/60-7.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="35">
   <si>
     <t xml:space="preserve">Expected Outcome</t>
   </si>
@@ -231,28 +231,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,200 +449,217 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>456</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>789</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>987</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>654</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>545</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>658</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>895</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>895</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -664,146 +685,146 @@
   <dimension ref="A2:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>456</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>789</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>987</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>654</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>345</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>321</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -826,95 +847,95 @@
   <dimension ref="A2:E6"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>545</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>658</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>895</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -937,61 +958,61 @@
   <dimension ref="A2:E4"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>345</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>321</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>34</v>
       </c>
     </row>

--- a/outputs/60-7.xlsx
+++ b/outputs/60-7.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="35">
   <si>
     <t xml:space="preserve">Expected Outcome</t>
   </si>
@@ -91,6 +91,24 @@
     <t xml:space="preserve">MNO</t>
   </si>
   <si>
+    <t xml:space="preserve">Quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PQR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As Needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recon 5</t>
   </si>
   <si>
@@ -100,34 +118,16 @@
     <t xml:space="preserve">MJE 6</t>
   </si>
   <si>
-    <t xml:space="preserve">As Needed</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arron</t>
   </si>
   <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
     <t xml:space="preserve">Other 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Quarterly</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Peter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PQR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STU</t>
   </si>
 </sst>
 </file>
@@ -449,7 +449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
@@ -580,16 +580,16 @@
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>345</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>545</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
@@ -597,50 +597,50 @@
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>658</v>
+        <v>321</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>124</v>
+        <v>545</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>895</v>
+        <v>658</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>31</v>
@@ -648,19 +648,70 @@
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>895</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>345</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>321</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>895</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -805,27 +856,27 @@
         <v>345</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>321</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +927,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>545</v>
@@ -885,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -893,50 +944,50 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>658</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>124</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>895</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -993,27 +1044,27 @@
         <v>345</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>321</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
